--- a/artfynd/A 56826-2025 artfynd.xlsx
+++ b/artfynd/A 56826-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1123,32 +1123,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130216512</v>
+        <v>130217641</v>
       </c>
       <c r="B6" t="n">
-        <v>80228</v>
+        <v>79095</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1158,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>474205</v>
+        <v>474290</v>
       </c>
       <c r="R6" t="n">
-        <v>6654526</v>
+        <v>6654608</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1193,7 +1193,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1230,32 +1230,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130217641</v>
+        <v>130216512</v>
       </c>
       <c r="B7" t="n">
-        <v>79095</v>
+        <v>80228</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1265,10 +1265,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>474290</v>
+        <v>474205</v>
       </c>
       <c r="R7" t="n">
-        <v>6654608</v>
+        <v>6654526</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1334,6 +1334,414 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>130243009</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57741</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Hassikmossen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>474404</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6654360</v>
+      </c>
+      <c r="S8" t="n">
+        <v>20</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhackad gran</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>130243777</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79095</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Hassikmossen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>474262</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6654628</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>130243155</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57741</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Hassikmossen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>474225</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6654708</v>
+      </c>
+      <c r="S10" t="n">
+        <v>20</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>130243354</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57741</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Hassikmossen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>474256</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6654567</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 56826-2025 artfynd.xlsx
+++ b/artfynd/A 56826-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130217994</v>
       </c>
       <c r="B2" t="n">
-        <v>80228</v>
+        <v>80313</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>130217338</v>
       </c>
       <c r="B3" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>130216714</v>
       </c>
       <c r="B4" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>130217323</v>
       </c>
       <c r="B5" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>130217641</v>
       </c>
       <c r="B6" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>130216512</v>
       </c>
       <c r="B7" t="n">
-        <v>80228</v>
+        <v>80313</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>130243009</v>
       </c>
       <c r="B8" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>130243777</v>
       </c>
       <c r="B9" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>130243155</v>
       </c>
       <c r="B10" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>130243354</v>
       </c>
       <c r="B11" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 56826-2025 artfynd.xlsx
+++ b/artfynd/A 56826-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,45 +675,50 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130217994</v>
+        <v>130217338</v>
       </c>
       <c r="B2" t="n">
-        <v>80313</v>
+        <v>57826</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hassikmossen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>474414</v>
+        <v>474253</v>
       </c>
       <c r="R2" t="n">
-        <v>6654361</v>
+        <v>6654692</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -745,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhackad gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +792,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130217338</v>
+        <v>130216714</v>
       </c>
       <c r="B3" t="n">
         <v>57826</v>
@@ -813,7 +823,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -822,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>474253</v>
+        <v>474242</v>
       </c>
       <c r="R3" t="n">
-        <v>6654692</v>
+        <v>6654562</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -857,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,12 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:20</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhackad gran</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,7 +904,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130216714</v>
+        <v>130217323</v>
       </c>
       <c r="B4" t="n">
         <v>57826</v>
@@ -939,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>474242</v>
+        <v>474247</v>
       </c>
       <c r="R4" t="n">
-        <v>6654562</v>
+        <v>6654781</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -974,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130217323</v>
+        <v>130217641</v>
       </c>
       <c r="B5" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1022,39 +1027,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hassikmossen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>474247</v>
+        <v>474290</v>
       </c>
       <c r="R5" t="n">
-        <v>6654781</v>
+        <v>6654608</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,32 +1123,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130217641</v>
+        <v>130216512</v>
       </c>
       <c r="B6" t="n">
-        <v>79180</v>
+        <v>80313</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1158,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>474290</v>
+        <v>474205</v>
       </c>
       <c r="R6" t="n">
-        <v>6654608</v>
+        <v>6654526</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1193,7 +1193,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1230,48 +1230,53 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130216512</v>
+        <v>130243009</v>
       </c>
       <c r="B7" t="n">
-        <v>80313</v>
+        <v>57826</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hassikmossen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>474205</v>
+        <v>474404</v>
       </c>
       <c r="R7" t="n">
-        <v>6654526</v>
+        <v>6654360</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1295,22 +1300,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>13:27</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>13:27</t>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhackad gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1337,10 +1337,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130243009</v>
+        <v>130243777</v>
       </c>
       <c r="B8" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1348,42 +1348,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hassikmossen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474404</v>
+        <v>474262</v>
       </c>
       <c r="R8" t="n">
-        <v>6654360</v>
+        <v>6654628</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1413,11 +1408,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-12-16</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhackad gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1444,10 +1434,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130243777</v>
+        <v>130243155</v>
       </c>
       <c r="B9" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1455,37 +1445,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hassikmossen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>474262</v>
+        <v>474225</v>
       </c>
       <c r="R9" t="n">
-        <v>6654628</v>
+        <v>6654708</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1541,7 +1536,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130243155</v>
+        <v>130243354</v>
       </c>
       <c r="B10" t="n">
         <v>57826</v>
@@ -1572,7 +1567,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1581,13 +1576,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>474225</v>
+        <v>474256</v>
       </c>
       <c r="R10" t="n">
-        <v>6654708</v>
+        <v>6654567</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1640,108 +1635,6 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>130243354</v>
-      </c>
-      <c r="B11" t="n">
-        <v>57826</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Hassikmossen, Dlr</t>
-        </is>
-      </c>
-      <c r="Q11" t="n">
-        <v>474256</v>
-      </c>
-      <c r="R11" t="n">
-        <v>6654567</v>
-      </c>
-      <c r="S11" t="n">
-        <v>10</v>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>Ludvika</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>Säfsnäs</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2025-12-16</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>2025-12-16</t>
-        </is>
-      </c>
-      <c r="AD11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="inlineStr"/>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>Tobias Hellberg</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>Tobias Hellberg</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 56826-2025 artfynd.xlsx
+++ b/artfynd/A 56826-2025 artfynd.xlsx
@@ -1019,7 +1019,7 @@
         <v>130217641</v>
       </c>
       <c r="B5" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>130243777</v>
       </c>
       <c r="B7" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 56826-2025 artfynd.xlsx
+++ b/artfynd/A 56826-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130217338</v>
       </c>
       <c r="B2" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>130216714</v>
       </c>
       <c r="B3" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>130217323</v>
       </c>
       <c r="B4" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>130217641</v>
       </c>
       <c r="B5" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>130243009</v>
       </c>
       <c r="B6" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>130243777</v>
       </c>
       <c r="B7" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>130243155</v>
       </c>
       <c r="B8" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>130243354</v>
       </c>
       <c r="B9" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 56826-2025 artfynd.xlsx
+++ b/artfynd/A 56826-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130217338</v>
       </c>
       <c r="B2" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>130216714</v>
       </c>
       <c r="B3" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>130217323</v>
       </c>
       <c r="B4" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>130217641</v>
       </c>
       <c r="B5" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>130243009</v>
       </c>
       <c r="B6" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>130243777</v>
       </c>
       <c r="B7" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>130243155</v>
       </c>
       <c r="B8" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>130243354</v>
       </c>
       <c r="B9" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 56826-2025 artfynd.xlsx
+++ b/artfynd/A 56826-2025 artfynd.xlsx
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130217338</v>
+        <v>130217641</v>
       </c>
       <c r="B2" t="n">
-        <v>57854</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hassikmossen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>474253</v>
+        <v>474290</v>
       </c>
       <c r="R2" t="n">
-        <v>6654692</v>
+        <v>6654608</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:20</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhackad gran</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,50 +782,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130216714</v>
+        <v>130243777</v>
       </c>
       <c r="B3" t="n">
-        <v>57854</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hassikmossen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>474242</v>
+        <v>474262</v>
       </c>
       <c r="R3" t="n">
-        <v>6654562</v>
+        <v>6654628</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -862,22 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>13:42</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>13:42</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130217323</v>
+        <v>130216714</v>
       </c>
       <c r="B4" t="n">
-        <v>57854</v>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -944,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>474247</v>
+        <v>474242</v>
       </c>
       <c r="R4" t="n">
-        <v>6654781</v>
+        <v>6654562</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -979,7 +954,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +964,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130217641</v>
+        <v>130216960</v>
       </c>
       <c r="B5" t="n">
-        <v>79211</v>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,34 +1002,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hassikmossen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>474290</v>
+        <v>474253</v>
       </c>
       <c r="R5" t="n">
-        <v>6654608</v>
+        <v>6654692</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1086,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1076,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhackad gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130243009</v>
+        <v>130217323</v>
       </c>
       <c r="B6" t="n">
-        <v>57854</v>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1154,7 +1139,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1163,13 +1148,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>474404</v>
+        <v>474247</v>
       </c>
       <c r="R6" t="n">
-        <v>6654360</v>
+        <v>6654781</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1193,17 +1178,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-19</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhackad gran</t>
+          <t>2025-12-19</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1230,10 +1220,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130243777</v>
+        <v>130243009</v>
       </c>
       <c r="B7" t="n">
-        <v>79211</v>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1241,37 +1231,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hassikmossen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>474262</v>
+        <v>474404</v>
       </c>
       <c r="R7" t="n">
-        <v>6654628</v>
+        <v>6654360</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1301,6 +1296,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhackad gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1330,7 +1330,7 @@
         <v>130243155</v>
       </c>
       <c r="B8" t="n">
-        <v>57854</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>130243354</v>
       </c>
       <c r="B9" t="n">
-        <v>57854</v>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
